--- a/FM-MN-07_BAND SAW-01.xlsx
+++ b/FM-MN-07_BAND SAW-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\From Iso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F152DF92-EBF5-4013-AF0E-8C09302712DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DA2121-F23B-4A14-8E39-F5AC72479C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{DE5370CA-647C-48FC-A6D6-FC5AAC313DA8}"/>
   </bookViews>
@@ -402,12 +402,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -429,19 +441,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1497,80 +1497,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="24" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="24"/>
-      <c r="AF1" s="24"/>
-      <c r="AG1" s="24"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
     </row>
     <row r="2" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="23"/>
-      <c r="AA2" s="23"/>
-      <c r="AB2" s="24" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
     </row>
     <row r="3" spans="1:33" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="16"/>
@@ -1608,49 +1608,49 @@
       <c r="AG3" s="14"/>
     </row>
     <row r="4" spans="1:33" s="9" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="33"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="33"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="33"/>
+      <c r="AG4" s="33"/>
     </row>
     <row r="5" spans="1:33" s="9" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="26"/>
-      <c r="B5" s="28"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="10">
         <v>1</v>
       </c>
@@ -1943,139 +1943,139 @@
     <row r="11" spans="1:33" ht="22.5" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="5"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
-      <c r="AA11" s="21"/>
-      <c r="AB11" s="21"/>
-      <c r="AC11" s="21"/>
-      <c r="AD11" s="21"/>
-      <c r="AE11" s="21"/>
-      <c r="AF11" s="21"/>
-      <c r="AG11" s="21"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="26"/>
+      <c r="S11" s="26"/>
+      <c r="T11" s="26"/>
+      <c r="U11" s="26"/>
+      <c r="V11" s="26"/>
+      <c r="W11" s="26"/>
+      <c r="X11" s="26"/>
+      <c r="Y11" s="26"/>
+      <c r="Z11" s="26"/>
+      <c r="AA11" s="26"/>
+      <c r="AB11" s="26"/>
+      <c r="AC11" s="26"/>
+      <c r="AD11" s="26"/>
+      <c r="AE11" s="26"/>
+      <c r="AF11" s="26"/>
+      <c r="AG11" s="26"/>
     </row>
     <row r="12" spans="1:33" ht="22.5" customHeight="1">
       <c r="B12" s="4"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="22"/>
-      <c r="AC12" s="22"/>
-      <c r="AD12" s="22"/>
-      <c r="AE12" s="22"/>
-      <c r="AF12" s="22"/>
-      <c r="AG12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="23"/>
+      <c r="W12" s="23"/>
+      <c r="X12" s="23"/>
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="23"/>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="23"/>
+      <c r="AC12" s="23"/>
+      <c r="AD12" s="23"/>
+      <c r="AE12" s="23"/>
+      <c r="AF12" s="23"/>
+      <c r="AG12" s="23"/>
     </row>
     <row r="13" spans="1:33" ht="22.5" customHeight="1">
       <c r="B13" s="4"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="30"/>
-      <c r="AC13" s="30"/>
-      <c r="AD13" s="30"/>
-      <c r="AE13" s="30"/>
-      <c r="AF13" s="30"/>
-      <c r="AG13" s="30"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+      <c r="AG13" s="22"/>
     </row>
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="B14" s="4"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="22"/>
-      <c r="AC14" s="22"/>
-      <c r="AD14" s="22"/>
-      <c r="AE14" s="22"/>
-      <c r="AF14" s="22"/>
-      <c r="AG14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="23"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="23"/>
+      <c r="AF14" s="23"/>
+      <c r="AG14" s="23"/>
     </row>
     <row r="15" spans="1:33" ht="19.5" customHeight="1">
       <c r="B15" s="20" t="s">
@@ -2083,38 +2083,38 @@
       </c>
     </row>
     <row r="16" spans="1:33" ht="342" customHeight="1">
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="31"/>
-      <c r="V16" s="31"/>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="31"/>
-      <c r="AA16" s="31"/>
-      <c r="AB16" s="31"/>
-      <c r="AC16" s="31"/>
-      <c r="AD16" s="31"/>
-      <c r="AE16" s="31"/>
-      <c r="AF16" s="31"/>
-      <c r="AG16" s="31"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="24"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="24"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="24"/>
     </row>
     <row r="17" spans="3:33" ht="21" customHeight="1">
       <c r="AA17" s="3"/>
@@ -2126,28 +2126,84 @@
       <c r="AG17" s="34"/>
     </row>
     <row r="18" spans="3:33" ht="29.25" customHeight="1">
-      <c r="AB18" s="32" t="s">
+      <c r="AB18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="AC18" s="32"/>
-      <c r="AD18" s="32"/>
-      <c r="AE18" s="32"/>
-      <c r="AF18" s="32"/>
-      <c r="AG18" s="32"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="25"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="25"/>
     </row>
     <row r="19" spans="3:33" ht="14.25" customHeight="1">
       <c r="C19" s="2"/>
-      <c r="AB19" s="33" t="s">
+      <c r="AB19" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="AC19" s="33"/>
-      <c r="AD19" s="33"/>
-      <c r="AE19" s="33"/>
-      <c r="AF19" s="33"/>
-      <c r="AG19" s="33"/>
+      <c r="AC19" s="21"/>
+      <c r="AD19" s="21"/>
+      <c r="AE19" s="21"/>
+      <c r="AF19" s="21"/>
+      <c r="AG19" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="AE11:AE12"/>
+    <mergeCell ref="AF11:AF12"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="AB19:AG19"/>
     <mergeCell ref="AB17:AG17"/>
     <mergeCell ref="AC13:AC14"/>
@@ -2164,62 +2220,6 @@
     <mergeCell ref="AG13:AG14"/>
     <mergeCell ref="B16:AG16"/>
     <mergeCell ref="AB18:AG18"/>
-    <mergeCell ref="AC11:AC12"/>
-    <mergeCell ref="AD11:AD12"/>
-    <mergeCell ref="AE11:AE12"/>
-    <mergeCell ref="AF11:AF12"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="AB11:AB12"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="AA11:AA12"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="AG11:AG12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
